--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data and Software Engineer I (API) (32_2026.1)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Databricks, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3fc7cad7b621a95</t>
+          <t>https://www.indeed.com/viewjob?jk=6ced5764d3537ea0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data and Software Engineer I (API) (32_2026.1)</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Hitachi Digital Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Databricks, GCP</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ced5764d3537ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5df2e993fb881155</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>(USA) Senior, Data Engineer - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df2e993fb881155</t>
+          <t>https://www.indeed.com/viewjob?jk=6bedd59c754ec609</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Engineer - Senior Software Engineer</t>
+          <t>Plan Sponsor Reporting Technologist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bedd59c754ec609</t>
+          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Plan Sponsor Reporting Technologist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Associa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe7366cb944d55d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associa</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe7366cb944d55d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Senior Backend Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Auction Technology Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df47aafd3009ff</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (IT Data Management Entry In-Training to Journey) DOH8822</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, HBase, Spark, Kafka, SQL Server</t>
+          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e85dc13d85ca930</t>
+          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
         </is>
       </c>
     </row>
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Kafka, SQL Server, PostgreSQL, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce804f8ce3a73549</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Database Administrator-1</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Talend, CI/CD</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d609df3b9f61295</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Database Administrator-1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d609df3b9f61295</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HOPE MEDIA GROUP</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14473c6bb0ab2439</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,42 +3811,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>(1357) Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4eebde6b6cf3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496d31cfec6658e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Databricks engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75cc0f18e33a178</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-1</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Economist III - Long Term Impact</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Docker, Airflow</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f28cdebb849a19</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Architect-1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Product Security Associate (College Grad)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>
@@ -5257,6 +5257,181 @@
       <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Alight Solutions</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Miller Cooper</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2778,52 +2778,52 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,69 +3251,69 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Database Administrator-1</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Talend, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d609df3b9f61295</t>
+          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Senior Database Administrator-1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Redshift, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=2d609df3b9f61295</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,42 +3881,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,59 +3926,59 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>(1357) Senior Reliability Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-1</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Product Security Associate (College Grad)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Azure Databricks Architect-1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Product Security Associate (College Grad)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, dbt, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b808411d8487a58f</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
@@ -5403,17 +5403,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Miller Cooper</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,17 +5421,157 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dfed33e248e8fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Saviynt Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Konrad Group</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Teradata Developer-4</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Softnice</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>North Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Platform Enablement</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Auction Technology Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df47aafd3009ff</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Senior Backend Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Auction Technology Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df47aafd3009ff</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4210181db0262688</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9f0c027bd53428</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, PA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a0ae84f6b87980</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9f0c027bd53428</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a0ae84f6b87980</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9fbf9321e91c82</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9fbf9321e91c82</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
+          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>AWS AI &amp; DevOps Intern</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,69 +2796,69 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,24 +3251,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,69 +3951,69 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,17 +4581,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
+          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
+          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-1</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
+          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Azure Databricks Architect-1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Product Security Associate (College Grad)</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
+          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Security Associate (College Grad)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,15 +5561,50 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Softnice</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>North Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associa</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe7366cb944d55d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Senior Backend Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Auction Technology Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df47aafd3009ff</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Platform Enablement</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Auction Technology Group</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df47aafd3009ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Neubus, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9f0c027bd53428</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9f0c027bd53428</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, PA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, ETL, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a0ae84f6b87980</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS AI &amp; DevOps Intern</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f896c6da0dfabb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Numero Data LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,24 +3251,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, SQS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=731a813c3cc4a70a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d56bb5a0c74a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,69 +3951,69 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Network Automation Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
         </is>
       </c>
     </row>
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,17 +4581,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
@@ -4808,17 +4808,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
+          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IT Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tungsten Automation</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Databricks Architect-1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-1</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Product Security Associate (College Grad)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>IT Integration Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Tungsten Automation</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
         </is>
       </c>
     </row>
@@ -5607,6 +5607,41 @@
       <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Product Security Associate (College Grad)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Platform Enablement</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Auction Technology Group</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df47aafd3009ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,29 +2201,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9f0c027bd53428</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9fbf9321e91c82</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1544d3d51cf528c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2816b3964dd4df</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Numero Data LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
         </is>
       </c>
     </row>
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Numero Data LLC</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b784b421e2120a24</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Database Administrator-1</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Talend, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d609df3b9f61295</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,42 +3671,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731a813c3cc4a70a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,42 +3926,42 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da661d8fb0ece801</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03d32c795783e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce987d03cd6c59b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,42 +4371,42 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a5cf8eb1fd67c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9346f3db3d75bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,172 +4521,172 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,67 +4801,67 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896402c926af3a49</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI and Automation Deployment Intern (Hybrid - Reston, VA Office)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,59 +4871,59 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89aebc7ded0cfa06</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58780039e9e611ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>North Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,707 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Airvet</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Security Analytics Data Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Glassbox</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>TECHSTRA SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Observability Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Klaviyo</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Azure Databricks Architect-1</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70788055152254cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Architect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17cf508536512d03</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6af7b3b86256a1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Plaud</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>University of Maryland Global Campus</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Redwood Logistics</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Saviynt Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Konrad Group</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>IT Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Tungsten Automation</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>ECS, IAM, Scala, Snowflake, SQL Server, NoSQL, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb56bd3754295d02</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Teradata Developer-4</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Softnice</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>North Chesterfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Product Security Associate (College Grad)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=689ae505cda9c946</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,77 +741,77 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,29 +2201,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef65db0c8cded69</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,69 +2551,69 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Numero Data LLC</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Numero Data LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee26f17ffea2401</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9be3c418bc5646</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,69 +3671,69 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,29 +3951,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,69 +4371,69 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,15 +4931,120 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Teradata Developer-4</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Softnice</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>North Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer (Only W2)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,77 +2411,77 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=a35418db0adaf400</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Numero Data LLC</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60d9899ce76c629</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Numero Data LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb1becaa3bb4909</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,42 +3706,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>(1357) Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed37c67470dc51b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,42 +4406,42 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,59 +4521,59 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3b123f509108b3</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
@@ -5047,6 +5047,111 @@
       <c r="G132" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Saviynt Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>University of Maryland Global Campus</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Adelphi, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Konrad Group</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Only W2)</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer (Only W2)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Numero Data LLC</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Numero Data LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>KSBJ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>(1357) Senior Reliability Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,19 +3961,19 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>(1357) Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
@@ -4563,17 +4563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,69 +2726,69 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Numero Data LLC</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Numero Data LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
@@ -3863,25 +3863,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>(1357) Senior Reliability Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,19 +3996,19 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>(1357) Senior Reliability Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Engineer - Mobility</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,52 +4546,52 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Glassbox</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,15 +5141,85 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Teradata Developer-4</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Softnice</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>North Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Plan Sponsor Reporting Technologist</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Google Cloud Platform, GCP, Hadoop, HDFS, Hive</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cab1d45df63628e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Sr. Data Engineer (Only W2)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Only W2)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Solution Architect/System Architect (US)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Trinetix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=70339cff36501a53</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Numero Data LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fd739375824cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Rice Engineering</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5908ca8b0f7aacbd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a61e3564cb83914</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=29e7697b5567a66e</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>North Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Only W2)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solution Architect/System Architect (US)</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trinetix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70339cff36501a53</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35418db0adaf400</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,24 +2656,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,59 +2736,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Rice University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=29c39de545706a17</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rice Engineering</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a61e3564cb83914</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Rice Engineering</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,77 +3216,77 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=4a61e3564cb83914</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e7697b5567a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Copperpoddigital Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KSBJ</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fab7a2259449584</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>(1357) Senior Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c8f5bbb025388b</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3fa3292f16042b</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc9d71c38d6760</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Mobility</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a61acd22258533d</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5a7c704ef11e31</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,137 +4311,137 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,59 +4556,59 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Glassbox</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, NoSQL, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7eed342df94f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>North Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4905,321 +4905,6 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Plaud</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Redwood Logistics</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Teradata Developer-4</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Softnice</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>North Chesterfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Saviynt Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>University of Maryland Global Campus</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Konrad Group</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
         </is>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Hadoop, Hive, Impala, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fe852730ed983b</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9916c3b5d3e4d372</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Senior Systems Engineer, UDS Data Management</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,24 +2586,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,94 +2771,94 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b0abfc59f8f9d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f86429bfad3f926</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c39de545706a17</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Rice University</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,77 +3041,77 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=29c39de545706a17</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,94 +3156,94 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rice Engineering</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a61e3564cb83914</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Disaster Recovery Specialist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Copperpoddigital Inc</t>
+          <t>Mi-Case</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,129 +3646,129 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8180238fd0566</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Performance Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chestnut Hill, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=704b47191373c7ad</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
@@ -3933,17 +3933,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Full-Stack Senior Software Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,42 +4276,42 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ef7cc52780120</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Senior Observability Platform Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
         </is>
       </c>
     </row>
@@ -4423,17 +4423,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist - Pricing and Promotions Optimization</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2dd0084730de1d4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist - Pricing and Promotions Optimization</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac1b66db18d2c42</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>North Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Software Engineer (AI Enablement)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,77 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>University of Maryland Global Campus</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Konrad Group</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, Data Modeling, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7de0ea1f90bea9f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Solution Architect/System Architect (US)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Trinetix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,69 +2166,69 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=70339cff36501a53</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6610ed807a1c6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
@@ -2323,25 +2323,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=870984d57341ef57</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=a35418db0adaf400</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,24 +2586,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Information Technology - BI Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>TCC Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Fishers, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Rice University</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=29c39de545706a17</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Rice Engineering</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=4a61e3564cb83914</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,77 +3041,77 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c39de545706a17</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Sr Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a3a619f61b04b</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=29e7697b5567a66e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Database Administrator-1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d609df3b9f61295</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Disaster Recovery Specialist</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mi-Case</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb5a54ccdddc65e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Performance Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chestnut Hill, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704b47191373c7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Senior Performance Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Chestnut Hill, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=704b47191373c7ad</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,129 +4136,129 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Observability Platform Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db8b13f873a0ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Scientist - Pricing and Promotions Optimization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2dd0084730de1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Scientist - Pricing and Promotions Optimization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac1b66db18d2c42</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
+          <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Scientist - Pricing and Promotions Optimization</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>North Chesterfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0583738bd2a761d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2dd0084730de1d4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Data Scientist - Pricing and Promotions Optimization</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac1b66db18d2c42</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Plaud</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,15 +4826,120 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Alight Solutions</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Enablement)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Redwood Logistics</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data and Software Engineer I (API) (32_2026.1)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Databricks, GCP</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ced5764d3537ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=325e4219bc2f7757</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ML Ops Engineer</t>
+          <t>Senior Data and Software Engineer I (API) (32_2026.1)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Databricks, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df2e993fb881155</t>
+          <t>https://www.indeed.com/viewjob?jk=6ced5764d3537ea0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Engineer - Senior Software Engineer</t>
+          <t>(USA) Senior, Data Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b555f123481de91</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect/System Architect (US)</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trinetix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70339cff36501a53</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Colombia (only) - Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>CADEX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,139 +2271,139 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=870984d57341ef57</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, DataOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870984d57341ef57</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35418db0adaf400</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Software Engineer Sys 3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Software Engineer Sr.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,24 +2551,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PPC Partners Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,102 +2701,102 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Information Technology - BI Data Architect</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TCC Verizon Authorized Retailer</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fishers, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a149a432f720bb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Data Services</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c39de545706a17</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rice Engineering</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a61e3564cb83914</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Engineer - Container Platform (Primary)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Business System Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Hive, Sqoop, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1aa56bb760b5544</t>
+          <t>https://www.indeed.com/viewjob?jk=d1dad4f5aba9b286</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,147 +3391,147 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e7697b5567a66e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Database Administrator-1</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, Talend, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d609df3b9f61295</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,94 +3611,94 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d985dfab97c4672d</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Performance Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chestnut Hill, MA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704b47191373c7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,77 +3916,77 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,137 +3996,137 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,119 +4136,119 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,402 +4546,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Data Scientist - Pricing and Promotions Optimization</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2dd0084730de1d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Scientist - Pricing and Promotions Optimization</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Wellesley, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac1b66db18d2c42</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Data Warehouse/BI Developer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>ThinkMirum, Inc.</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Teradata Developer-4</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Saviynt Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>University of Maryland Global Campus</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Plaud</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI Enablement)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Redwood Logistics</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, CI/CD, AKS, Airflow</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0a71f110d4bcaf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Engineer - Full Stack</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bedd59c754ec609</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84539e9d32b8f8db</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=870984d57341ef57</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Colombia (only) - Remote</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CADEX</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc87d5a21e8908c6</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, DataOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870984d57341ef57</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer Sys 3</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2477,116 +2477,116 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Lake Storage, Spark, Scala, Spark Streaming, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b87979ce36653f6</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer Sr.</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694acb45c2cc0b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
+          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Digital Analytics Customer Experience (CX) Engineer</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fcbbc0dd03080c</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PPC Partners Inc.</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Snowflake, Oracle, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f64c130369ad2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Services</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2b768ed31bba34</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Systems Engineer - Container Platform (Primary)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Business System Solutions</t>
+          <t>TruMinds Technology Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Tableau, MLOps, MLflow, Docker, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96abe73e052d5071</t>
+          <t>https://www.indeed.com/viewjob?jk=e03879d64f0d66b6</t>
         </is>
       </c>
     </row>
@@ -3233,95 +3233,95 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Java Backend with Databricks experiance</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,164 +3786,164 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Security Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=c1785b277f2b3b5c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4345,216 +4345,6 @@
         </is>
       </c>
       <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Warehouse/BI Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>ThinkMirum, Inc.</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Teradata Developer-4</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Plaud</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=172852e482d4c615</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Alight Solutions</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccbe5961b0d1ed9</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
         </is>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ocean Blue Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Data Engineer, IT Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Sales Analytics (GTM Data Engineering)</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721d4b934257a77e</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,69 +2656,69 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>AIML Services- Data Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e5ffc39cf3d166</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>TruMinds Technology Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Tableau, MLOps, MLflow, Docker, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=e03879d64f0d66b6</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1dad4f5aba9b286</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TruMinds Technology Inc</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Tableau, MLOps, MLflow, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,42 +3191,42 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03879d64f0d66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1dad4f5aba9b286</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Java Backend with Databricks experiance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b862550824c4cea</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1785b277f2b3b5c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Security Analytics Data Engineer</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Spark, Scala, Kafka, NoSQL, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca444d34471a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Allegiant Air</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1785b277f2b3b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>University of Maryland Global Campus</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
+          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>University of Maryland Global Campus</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Teradata Developer-4</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4275,76 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Plaud</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
         </is>

--- a/results/job_matches_2026-02-25.xlsx
+++ b/results/job_matches_2026-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer I (37_2026.1)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7933ce6e87f7544</t>
+          <t>https://www.indeed.com/viewjob?jk=325e4219bc2f7757</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=325e4219bc2f7757</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data and Software Engineer I (API) (32_2026.1)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Databricks, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ced5764d3537ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
         </is>
       </c>
     </row>
@@ -653,11 +653,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -666,82 +666,82 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ocean Blue Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1820f8d0d8314d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ccb9adf6566f3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50332f23365d6c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488784d73124ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a83a03051de71cc</t>
+          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf9f1be1b3cebb3</t>
+          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09088ced465b49f7</t>
+          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918a7e3c1ab3b499</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df850d0800211a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f6cf05adf06982</t>
+          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49351622325c642d</t>
+          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cb630284635d10</t>
+          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18fe79343696c2</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01fcf56429b22f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d3942f25a95dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f41f660f48774</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8c99e610dc718a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe48df16882c48ff</t>
+          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ab104d579f6157</t>
+          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb69f10163f7e52</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff48f763950a943a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41daa222a6c0eb65</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b513eec114560369</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1fc91c2f3af434</t>
+          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd42a0e9f6369fb</t>
+          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce8108c4c6139a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb1399157ed987a</t>
+          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa27179e71f1d215</t>
+          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487287ab40eadad6</t>
+          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a4b18b4f729cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5156ae4f3304f436</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1291f0caedc31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c38f857835e4e55</t>
+          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bf91f82d524c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7a7b948aeaf749</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa6956cd2874889</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Senior Databricks Developer-4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,172 +1966,172 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ced1716ea9d344</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6072c3cca7eb88</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, RDS, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e5e0e8fb1f2fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=870984d57341ef57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-4</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9ed7f399638350</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, IAM, RDS, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ec5a38573c3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870984d57341ef57</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Identity Shield &amp; Consumer Fraud - FDP</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a541a3b49011d60</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2316,137 +2316,137 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd32825b07168a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a073dd45695fc17b</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Flywheel Energy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a98bbc96397eaf9</t>
+          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III, Backend - Recs Infrastructure</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Flywheel Energy</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff21e0f44745194</t>
+          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer, IT Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b03a3fc26187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=123628d5e21a6f89</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend - Recs Infrastructure</t>
+          <t>Senior Platform Engineer-</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Netsmart Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64c7b902fd5f682</t>
+          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Senior Engineer II - International Marketing Technology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=d1dad4f5aba9b286</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytical Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Azure, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33d86f281463c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Merlin Labs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25ec63d2a45d72c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>TruMinds Technology Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,112 +2866,112 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Tableau, MLOps, MLflow, Docker, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41cbea8637a10d68</t>
+          <t>https://www.indeed.com/viewjob?jk=e03879d64f0d66b6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AIML Services- Data Platform Engineer</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, MLflow, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ad64f2466c8d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer II - International Marketing Technology</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a5ab49999f0089</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Operations</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ebeb9e75e44d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytical Engineer</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8d280f0f8b9b62</t>
+          <t>https://www.indeed.com/viewjob?jk=63d81ec56ed45b4c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Scientist – AI &amp; Machine Learning Systems (Dublin, CA)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Merlin Labs</t>
+          <t>SavvyMoney</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f002df8ebe456c</t>
+          <t>https://www.indeed.com/viewjob?jk=e01821abea23411c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, PostgreSQL, Tableau, Splunk, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7833a34175870f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TruMinds Technology Inc</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Tableau, MLOps, MLflow, Docker, Airflow</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03879d64f0d66b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1dad4f5aba9b286</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5be230e591e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Sr Power BI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c064cf7becc7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Heads Up Technologies</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a47a44d6a3f091</t>
+          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Performance Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Chestnut Hill, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29f4a8356c6b860</t>
+          <t>https://www.indeed.com/viewjob?jk=704b47191373c7ad</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3faf055caa8c357</t>
+          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9944f1992e587dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Power BI Developer</t>
+          <t>AI Engineer, Business Operations</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>SK Life Science Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91012cb164e9d48a</t>
+          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af3b68e608e8a0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Allegiant Air</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Scala, SQL Server, Dimensional Modeling, ETL, Terraform</t>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1785b277f2b3b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Senior Data Engineer – AxiomSL Development</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – AxiomSL Development</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3517357605b9f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Teradata Developer-4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Engineer, Business Operations</t>
+          <t>Senior DevOps Engineer - San Francisco</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SK Life Science Inc.</t>
+          <t>Plaud</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Snowflake, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,287 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ea28bb19313647</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Airvet</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e51b2375febffa24</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Data Warehouse/BI Developer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>ThinkMirum, Inc.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Teradata Developer-4</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae339b7b464395c</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - San Francisco</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Plaud</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c543d32a8ba8e61f</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Saviynt Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Oracle, ELT, Splunk, Azure DevOps, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bfe8e53848754e</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>University of Maryland Global Campus</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=635921f4402acdff</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, MLOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f836fc84892ec33f</t>
         </is>
       </c>
     </row>
